--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122452403</v>
       </c>
       <c r="B2" t="n">
-        <v>56425</v>
+        <v>56430</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,282 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122511391</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56271</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björneborgsvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>548134</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6321920</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>122511393</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56290</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björneborgsvägen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>548134</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6321920</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kråksmåla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>wurb2024 AA-43 med Pettersson u384</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Katharina Ahlert</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -693,11 +693,6 @@
       <c r="E2" t="n">
         <v>100045</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Sångsvan</t>
-        </is>
-      </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>Cygnus cygnus</t>
@@ -821,11 +816,6 @@
       <c r="E3" t="n">
         <v>205998</v>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -958,11 +948,6 @@
       </c>
       <c r="E4" t="n">
         <v>205995</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122452403</v>
       </c>
       <c r="B2" t="n">
-        <v>56430</v>
+        <v>56434</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>100045</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -798,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122511391</v>
+        <v>122511393</v>
       </c>
       <c r="B3" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,25 +815,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -931,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122511393</v>
+        <v>122511391</v>
       </c>
       <c r="B4" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -943,25 +953,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122511393</v>
+        <v>122511391</v>
       </c>
       <c r="B3" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,30 +815,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122511391</v>
+        <v>122511393</v>
       </c>
       <c r="B4" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,30 +953,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122452403</v>
       </c>
       <c r="B2" t="n">
-        <v>56434</v>
+        <v>56435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -806,7 +806,7 @@
         <v>122511391</v>
       </c>
       <c r="B3" t="n">
-        <v>56275</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
         <v>122511393</v>
       </c>
       <c r="B4" t="n">
-        <v>56294</v>
+        <v>56295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122511391</v>
+        <v>122511393</v>
       </c>
       <c r="B3" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,30 +815,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122511393</v>
+        <v>122511391</v>
       </c>
       <c r="B4" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,30 +953,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122511393</v>
+        <v>122511391</v>
       </c>
       <c r="B3" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,30 +815,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122511391</v>
+        <v>122511393</v>
       </c>
       <c r="B4" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,30 +953,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">

--- a/artfynd/A 9561-2023 artfynd.xlsx
+++ b/artfynd/A 9561-2023 artfynd.xlsx
@@ -803,10 +803,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122511391</v>
+        <v>122511393</v>
       </c>
       <c r="B3" t="n">
-        <v>56370</v>
+        <v>56389</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,30 +815,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -941,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122511393</v>
+        <v>122511391</v>
       </c>
       <c r="B4" t="n">
-        <v>56389</v>
+        <v>56370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,30 +953,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
